--- a/data/trans_dic/P1429-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1429-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,14</t>
+          <t>0,2; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,52</t>
+          <t>1,11; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,23</t>
+          <t>2,22; 7,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,45</t>
+          <t>2,52; 7,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,11</t>
+          <t>1,86; 4,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,6</t>
+          <t>0,63; 2,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,82</t>
+          <t>1,07; 3,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,85</t>
+          <t>1,24; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,01</t>
+          <t>1,24; 2,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,58</t>
+          <t>4,78; 9,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,83</t>
+          <t>1,41; 4,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,41</t>
+          <t>2,03; 5,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,91</t>
+          <t>2,17; 4,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,21</t>
+          <t>2,6; 5,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,9</t>
+          <t>1,02; 3,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,91</t>
+          <t>1,04; 2,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,48</t>
+          <t>1,14; 2,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,41</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,57</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,56</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,47</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,64</t>
+          <t>2,27; 6,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,63</t>
+          <t>1,46; 5,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,26</t>
+          <t>0,37; 4,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,41</t>
+          <t>3,24; 6,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,7</t>
+          <t>1,27; 3,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,1</t>
+          <t>0,81; 3,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,24</t>
+          <t>0,28; 2,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,74</t>
+          <t>1,84; 3,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,47</t>
+          <t>0,83; 5,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,33</t>
+          <t>2,48; 6,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,19</t>
+          <t>5,24; 11,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,62</t>
+          <t>3,97; 9,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,39</t>
+          <t>6,35; 10,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,2</t>
+          <t>1,22; 3,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,43</t>
+          <t>2,71; 5,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,32</t>
+          <t>2,2; 5,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,94</t>
+          <t>3,87; 6,95</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,29</t>
+          <t>0,23; 2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,26</t>
+          <t>0,47; 4,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,81</t>
+          <t>1,8; 7,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,06</t>
+          <t>3,15; 6,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,49</t>
+          <t>0,24; 2,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,44</t>
+          <t>0,9; 3,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,2</t>
+          <t>2,03; 4,0</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,5</t>
+          <t>0,67; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,05</t>
+          <t>2,33; 7,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,87</t>
+          <t>0,79; 4,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,8</t>
+          <t>0,81; 4,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,49</t>
+          <t>4,31; 8,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,92</t>
+          <t>1,11; 3,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,41</t>
+          <t>0,38; 2,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,97</t>
+          <t>0,75; 3,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,26</t>
+          <t>2,8; 5,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,55</t>
+          <t>0,16; 1,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,74</t>
+          <t>0,28; 1,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,66</t>
+          <t>0,25; 1,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,33</t>
+          <t>2,24; 5,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,31</t>
+          <t>3,06; 6,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,61</t>
+          <t>3,06; 6,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,08</t>
+          <t>4,48; 7,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,03</t>
+          <t>1,45; 3,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,33</t>
+          <t>1,69; 3,42</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,84</t>
+          <t>1,91; 3,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,5</t>
+          <t>2,61; 4,18</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,32</t>
+          <t>2,42; 5,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,29</t>
+          <t>0,36; 1,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,69</t>
+          <t>3,4; 6,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,29</t>
+          <t>2,4; 5,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,97</t>
+          <t>1,71; 4,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,55</t>
+          <t>2,52; 4,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,45</t>
+          <t>3,29; 5,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,74</t>
+          <t>1,37; 2,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,08</t>
+          <t>0,84; 2,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,54</t>
+          <t>1,62; 2,82</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,47</t>
+          <t>0,74; 1,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,44</t>
+          <t>0,06; 0,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,59</t>
+          <t>0,19; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,32</t>
+          <t>0,57; 1,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,0</t>
+          <t>3,6; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,8</t>
+          <t>3,36; 4,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,17</t>
+          <t>2,82; 4,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,01</t>
+          <t>4,21; 5,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,12</t>
+          <t>2,33; 3,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,5</t>
+          <t>1,78; 2,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,61; 2,28</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,0</t>
+          <t>2,54; 3,19</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12040</t>
         </is>
       </c>
     </row>
@@ -2219,52 +2219,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4034</t>
+          <t>0; 5269</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>694; 6659</t>
+          <t>651; 6108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3006; 14389</t>
+          <t>2903; 14076</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6392; 20758</t>
+          <t>6377; 21629</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6345; 21496</t>
+          <t>7269; 21694</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6035; 14802</t>
+          <t>5893; 14713</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2854; 13863</t>
+          <t>3343; 14918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6979; 22173</t>
+          <t>6202; 22511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7566; 22448</t>
+          <t>7199; 21688</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7868; 18118</t>
+          <t>7854; 17979</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18408</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4964</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 12001</t>
+          <t>0; 10811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4191</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4346</t>
+          <t>0; 4901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25183; 48285</t>
+          <t>24102; 47094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8202; 25236</t>
+          <t>7357; 24515</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9720; 28274</t>
+          <t>10607; 28232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11303; 25014</t>
+          <t>11712; 25547</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26290; 51970</t>
+          <t>25938; 50299</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10399; 29823</t>
+          <t>10451; 32192</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11001; 29867</t>
+          <t>10707; 30710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12200; 25435</t>
+          <t>12177; 26088</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17614</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4624</t>
+          <t>0; 4494</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,47 +2640,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4648</t>
+          <t>0; 4568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7494; 22271</t>
+          <t>7614; 22320</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5085; 19213</t>
+          <t>4974; 19117</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1915; 14334</t>
+          <t>1260; 13723</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10908; 22391</t>
+          <t>11562; 23627</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8354; 24210</t>
+          <t>8304; 22802</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5982; 20600</t>
+          <t>5370; 20582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1245; 14698</t>
+          <t>1812; 14389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12173; 24821</t>
+          <t>12390; 24988</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>41780</t>
         </is>
       </c>
     </row>
@@ -2843,52 +2843,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6050</t>
+          <t>0; 7384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2775; 20234</t>
+          <t>3115; 19655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8810; 23526</t>
+          <t>9212; 24639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20813; 43539</t>
+          <t>20393; 42842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15173; 37270</t>
+          <t>15382; 37829</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20032; 44657</t>
+          <t>26792; 45923</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8967; 23347</t>
+          <t>8881; 23504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20364; 41442</t>
+          <t>20672; 41691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17543; 40278</t>
+          <t>16638; 39810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27717; 54731</t>
+          <t>30782; 55265</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12356</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>436; 4093</t>
+          <t>469; 4332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>993; 8837</t>
+          <t>982; 9911</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3236; 14957</t>
+          <t>3950; 15775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7654</t>
+          <t>0; 7570</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7242; 14713</t>
+          <t>7140; 14968</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1118; 10252</t>
+          <t>992; 9626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3837; 14850</t>
+          <t>3905; 15003</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7662</t>
+          <t>0; 6578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8323; 16267</t>
+          <t>8799; 17305</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>20482</t>
         </is>
       </c>
     </row>
@@ -3259,52 +3259,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8347</t>
+          <t>0; 8038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2095; 9426</t>
+          <t>1816; 8244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6231; 19618</t>
+          <t>6470; 20072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2121; 13547</t>
+          <t>2186; 12504</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2940; 13106</t>
+          <t>2214; 13244</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11233; 21762</t>
+          <t>11336; 21760</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6303; 21493</t>
+          <t>6118; 20092</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2104; 13330</t>
+          <t>2114; 12903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3373; 15948</t>
+          <t>4006; 16353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14667; 27653</t>
+          <t>14952; 27740</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>48340</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>999; 9547</t>
+          <t>955; 8637</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5982</t>
+          <t>0; 6424</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2020; 11409</t>
+          <t>1820; 11535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1651; 10277</t>
+          <t>1803; 11502</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14690; 34038</t>
+          <t>14311; 32463</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21605; 43817</t>
+          <t>21209; 44387</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22205; 45693</t>
+          <t>21163; 44059</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16280; 51383</t>
+          <t>34303; 55312</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17841; 37970</t>
+          <t>18134; 37882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22067; 45158</t>
+          <t>22959; 46334</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26475; 51758</t>
+          <t>25808; 50287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23257; 51306</t>
+          <t>38634; 61946</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>35261</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17321; 39554</t>
+          <t>18000; 38691</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6278</t>
+          <t>0; 6341</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5179</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1526; 11935</t>
+          <t>2847; 12064</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26181; 52433</t>
+          <t>26665; 51545</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20019; 43498</t>
+          <t>19750; 41570</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12671; 32823</t>
+          <t>14112; 33627</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18272; 32493</t>
+          <t>20918; 37033</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52016; 83170</t>
+          <t>50250; 83120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20410; 43809</t>
+          <t>21943; 44484</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14184; 33418</t>
+          <t>13456; 33189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17752; 41759</t>
+          <t>26343; 45834</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24797; 48276</t>
+          <t>24124; 46684</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2057; 15112</t>
+          <t>2053; 16314</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6004; 20052</t>
+          <t>6567; 20549</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19725; 45696</t>
+          <t>20019; 43297</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>121146; 169092</t>
+          <t>121541; 169876</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>119238; 170426</t>
+          <t>119540; 170831</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>101099; 147982</t>
+          <t>100010; 146917</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>133684; 182674</t>
+          <t>156533; 197422</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>153714; 207773</t>
+          <t>155055; 206130</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123147; 174630</t>
+          <t>124345; 175054</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112228; 159314</t>
+          <t>111519; 158527</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>160015; 212931</t>
+          <t>183894; 231336</t>
         </is>
       </c>
     </row>
